--- a/Finalisation-concertation/ig/StructureDefinition-fr-inpatient-pharmaceutical-analysis-result.xlsx
+++ b/Finalisation-concertation/ig/StructureDefinition-fr-inpatient-pharmaceutical-analysis-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:36:59+00:00</t>
+    <t>2026-05-21T12:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Finalisation-concertation/ig/StructureDefinition-fr-inpatient-pharmaceutical-analysis-result.xlsx
+++ b/Finalisation-concertation/ig/StructureDefinition-fr-inpatient-pharmaceutical-analysis-result.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-inpatient-pharmaceutical-analysis-result</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-inpatient-pharmaceutical-analysis-result</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:38:31+00:00</t>
+    <t>2026-05-21T13:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,7 +650,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-pharmaceutical-intervention-devenir-code-value-set</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-pharmaceutical-intervention-devenir-code-value-set</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="business status"]</t>
@@ -939,7 +939,7 @@
     <t>Use to distinguish tasks on different activity queues.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-pharmaceutical-analysis-perfomer-type-value-set</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-pharmaceutical-analysis-perfomer-type-value-set</t>
   </si>
   <si>
     <t>Event.performer.role, Request.performerType</t>
@@ -1351,7 +1351,7 @@
     <t>Task.input.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-inpatient-medicationrequest)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-inpatient-medicationrequest)
 </t>
   </si>
   <si>
@@ -1468,7 +1468,7 @@
     <t>Task.output:result.value[x]</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-pharmaceutical-analysis-result-code-value-set</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-pharmaceutical-analysis-result-code-value-set</t>
   </si>
   <si>
     <t>Task.output:comment</t>
@@ -1543,7 +1543,7 @@
     <t>Task.output:type.value[x]</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-pharmaceutical-intervention-type-code-value-set</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-pharmaceutical-intervention-type-code-value-set</t>
   </si>
   <si>
     <t>Task.output:problem</t>
@@ -1582,7 +1582,7 @@
     <t>Task.output:problem.value[x]</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-pharmaceutical-intervention-problem-code-value-set</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-pharmaceutical-intervention-problem-code-value-set</t>
   </si>
   <si>
     <t>Task.output:suggestion</t>
@@ -1621,7 +1621,7 @@
     <t>Task.output:suggestion.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-inpatient-pharmaceutical-intervention-suggestion)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-inpatient-pharmaceutical-intervention-suggestion)
 </t>
   </si>
   <si>
@@ -1661,7 +1661,7 @@
     <t>Task.output:intervention.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-inpatient-pharmaceutical-analysis-result)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-inpatient-pharmaceutical-analysis-result)
 </t>
   </si>
 </sst>
@@ -2007,7 +2007,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="145.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="76.6015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="80.5703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="93.1640625" customWidth="true" bestFit="true"/>
